--- a/output/graficos_regionales_salud/plot_s_fonasa_a_2024_la_araucania.xlsx
+++ b/output/graficos_regionales_salud/plot_s_fonasa_a_2024_la_araucania.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 18:25</t>
+    <t xml:space="preserve">2026-09-09 19:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_salud/plot_s_fonasa_a_2024_la_araucania.xlsx
+++ b/output/graficos_regionales_salud/plot_s_fonasa_a_2024_la_araucania.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:19</t>
+    <t xml:space="preserve">2026-09-18 09:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_salud/plot_s_fonasa_a_2024_la_araucania.xlsx
+++ b/output/graficos_regionales_salud/plot_s_fonasa_a_2024_la_araucania.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:25</t>
+    <t xml:space="preserve">2026-09-25 10:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_salud/plot_s_fonasa_a_2024_la_araucania.xlsx
+++ b/output/graficos_regionales_salud/plot_s_fonasa_a_2024_la_araucania.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 10:52</t>
+    <t xml:space="preserve">2026-09-25 17:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_salud/plot_s_fonasa_a_2024_la_araucania.xlsx
+++ b/output/graficos_regionales_salud/plot_s_fonasa_a_2024_la_araucania.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 17:24</t>
+    <t xml:space="preserve">2026-10-05 06:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
